--- a/output/rolling_dy_results.xlsx
+++ b/output/rolling_dy_results.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rolling_Spillovers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Granger_Causality" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5667,735 +5665,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Cause</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Lag</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>F_stat</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>P_value</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Significant</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SP500</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.7228960985401377</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.486055656089793</v>
-      </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.5703722282891405</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.5658307108492273</v>
-      </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AGG</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7737692728522719</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.4620453020831123</v>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TLT</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9592094097941241</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.3841838152333341</v>
-      </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SP500</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.2288202366307604</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.7955884196894462</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.2176508112996156</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.8045132421334489</v>
-      </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AGG</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9309623207223374</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3951316607340203</v>
-      </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TLT</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.207072124851294</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.3002926521862705</v>
-      </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Bubble</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SP500</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.9172749919738425</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.4058560531059978</v>
-      </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Bubble</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.8606839729432808</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.4286980306284555</v>
-      </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Bubble</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AGG</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.6609856420908048</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.5205461291801068</v>
-      </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Bubble</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TLT</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.7091825145166164</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.4966552983162369</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Bubble</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SP500</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.02008047324085002</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.9801272497575571</v>
-      </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Bubble</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>VTI</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.02758239666028365</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.9728084786301878</v>
-      </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Bubble</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AGG</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.5365937606614395</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.5878794869626418</v>
-      </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Bubble</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ETH</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>TLT</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.8357274550195308</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.4391913837526613</v>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Crypto_Trad_Normal_Mean</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6.290863263434198</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Crypto_Trad_Bubble_Mean</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5.152367591448143</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Crypto_Trad_Difference_Absolute</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>-1.138495671986055</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Crypto_Trad_Difference_Relative_Pct</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-18.0976063905822</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Crypto_Trad_T_Stat</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.518506942451284</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Crypto_Trad_P_Value</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.0004884511038453562</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Crypto_Trad_P_Value_Bonferroni_Adjusted</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Crypto_Trad_Cohen_d</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>-0.3514194883070271</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Total_Normal_Mean</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>51.57343218978902</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Total_Bubble_Mean</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>47.40491232968228</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Total_Difference_Absolute</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-4.168519860106734</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Total_Difference_Relative_Pct</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-8.082688475660644</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Total_T_Stat</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5.34675265842306</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Total_P_Value</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.586690494780493e-07</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Total_P_Value_Bonferroni_Adjusted</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Total_Cohen_d</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>-0.5378151650444625</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>N_Normal_Windows</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>N_Bubble_Windows</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Bonferroni_Alpha</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>